--- a/Projekt Pitcernia.xlsx
+++ b/Projekt Pitcernia.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">COUNTIF(C:E, TRUE())</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>1</v>
@@ -810,8 +810,8 @@
         <v>0</v>
       </c>
       <c r="D8" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="E8" s="1" t="b">
         <f aca="false">FALSE()</f>
@@ -827,8 +827,8 @@
         <v>0</v>
       </c>
       <c r="D9" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="E9" s="1" t="b">
         <f aca="false">FALSE()</f>
@@ -844,7 +844,7 @@
       </c>
       <c r="G10" s="4" t="n">
         <f aca="false">G6*100/G2</f>
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -890,8 +890,8 @@
         <v>0</v>
       </c>
       <c r="D13" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="E13" s="1" t="b">
         <f aca="false">FALSE()</f>
@@ -1172,8 +1172,8 @@
         <v>0</v>
       </c>
       <c r="D31" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="E31" s="1" t="b">
         <f aca="false">FALSE()</f>
@@ -1189,8 +1189,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="E32" s="1" t="b">
         <f aca="false">FALSE()</f>

--- a/Projekt Pitcernia.xlsx
+++ b/Projekt Pitcernia.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">COUNTIF(C:E, TRUE())</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>1</v>
@@ -844,7 +844,7 @@
       </c>
       <c r="G10" s="4" t="n">
         <f aca="false">G6*100/G2</f>
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -997,8 +997,8 @@
         <v>0</v>
       </c>
       <c r="D20" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="E20" s="1" t="b">
         <f aca="false">FALSE()</f>
